--- a/data/trans_dic/P16A15-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,96</t>
+          <t>4,23; 7,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 14,8</t>
+          <t>9,76; 14,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 14,16</t>
+          <t>9,4; 14,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 16,47</t>
+          <t>11,6; 16,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,78</t>
+          <t>6,39; 10,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 16,66</t>
+          <t>11,39; 16,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,51</t>
+          <t>10,93; 16,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,82; 17,55</t>
+          <t>13,7; 17,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,61</t>
+          <t>5,88; 8,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 15,1</t>
+          <t>11,26; 14,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 14,54</t>
+          <t>10,93; 14,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,12; 16,45</t>
+          <t>13,29; 16,44</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,52</t>
+          <t>4,48; 7,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 12,41</t>
+          <t>8,12; 12,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,7</t>
+          <t>7,76; 11,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,11</t>
+          <t>4,36; 11,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 11,15</t>
+          <t>7,4; 11,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,78; 13,81</t>
+          <t>9,71; 13,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 14,23</t>
+          <t>10,05; 14,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 15,31</t>
+          <t>12,1; 15,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,81</t>
+          <t>6,25; 8,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,44; 12,32</t>
+          <t>9,38; 12,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 12,29</t>
+          <t>9,42; 12,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,96</t>
+          <t>7,16; 12,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,32</t>
+          <t>3,96; 7,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 11,6</t>
+          <t>7,01; 11,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,08</t>
+          <t>7,49; 11,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 14,82</t>
+          <t>10,03; 15,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,54</t>
+          <t>5,76; 9,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 15,44</t>
+          <t>10,37; 15,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 10,36</t>
+          <t>5,86; 10,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,66; 63,47</t>
+          <t>10,62; 67,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,82</t>
+          <t>5,22; 7,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 12,85</t>
+          <t>9,45; 12,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,29</t>
+          <t>7,41; 10,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,18; 49,25</t>
+          <t>11,22; 53,33</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,39</t>
+          <t>4,68; 7,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,29; 12,62</t>
+          <t>8,05; 12,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,29</t>
+          <t>5,93; 9,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,47</t>
+          <t>10,58; 14,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,5</t>
+          <t>5,42; 8,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 13,59</t>
+          <t>9,68; 13,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 12,73</t>
+          <t>8,85; 13,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,19</t>
+          <t>11,81; 16,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,55</t>
+          <t>5,42; 7,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 12,57</t>
+          <t>9,46; 12,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 10,54</t>
+          <t>7,87; 10,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 14,71</t>
+          <t>11,47; 14,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,64</t>
+          <t>5,02; 6,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,3</t>
+          <t>9,24; 11,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,37</t>
+          <t>8,5; 10,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,83</t>
+          <t>8,53; 12,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,8</t>
+          <t>6,98; 8,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 13,39</t>
+          <t>11,21; 13,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,91; 12,15</t>
+          <t>9,84; 12,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,43; 34,41</t>
+          <t>13,31; 32,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,52</t>
+          <t>6,32; 7,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 12,07</t>
+          <t>10,5; 12,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 10,98</t>
+          <t>9,45; 10,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,29; 24,35</t>
+          <t>12,19; 24,24</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29906; 55143</t>
+          <t>29311; 54036</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66983; 103732</t>
+          <t>68418; 103494</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64317; 95546</t>
+          <t>63407; 98425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72471; 104626</t>
+          <t>73702; 104358</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45941; 74223</t>
+          <t>43981; 72627</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78253; 115691</t>
+          <t>79059; 114348</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75463; 111066</t>
+          <t>73559; 110567</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93383; 118569</t>
+          <t>92554; 118369</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80898; 118942</t>
+          <t>81217; 118564</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155768; 210675</t>
+          <t>157139; 208226</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148839; 195974</t>
+          <t>147248; 195741</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>172055; 215645</t>
+          <t>174228; 215501</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43375; 72322</t>
+          <t>43043; 72518</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85533; 126360</t>
+          <t>82654; 122715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80341; 119578</t>
+          <t>79345; 119161</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60062; 144430</t>
+          <t>52008; 141963</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71072; 107987</t>
+          <t>71671; 107678</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>100368; 141828</t>
+          <t>99670; 141358</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>104634; 148456</t>
+          <t>104809; 150120</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>114355; 146664</t>
+          <t>115976; 147792</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121616; 170108</t>
+          <t>120728; 167439</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>193025; 251965</t>
+          <t>191784; 250064</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>194737; 253733</t>
+          <t>194530; 257100</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>147574; 278688</t>
+          <t>153933; 278718</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26866; 49679</t>
+          <t>26847; 50249</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54631; 87745</t>
+          <t>53036; 87444</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57575; 91740</t>
+          <t>56893; 89350</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70291; 104259</t>
+          <t>70579; 106265</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38628; 65231</t>
+          <t>39356; 66082</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80311; 119869</t>
+          <t>80475; 118619</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46637; 81339</t>
+          <t>46007; 79136</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>99413; 592006</t>
+          <t>99049; 633866</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71950; 106580</t>
+          <t>71083; 106766</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145073; 196950</t>
+          <t>144847; 196667</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>111168; 158896</t>
+          <t>114429; 156183</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>183007; 806016</t>
+          <t>183671; 872737</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45186; 69603</t>
+          <t>44129; 71954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78373; 119358</t>
+          <t>76174; 117381</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56003; 87079</t>
+          <t>55639; 87750</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97821; 134116</t>
+          <t>98066; 134176</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55553; 88329</t>
+          <t>56264; 89563</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>101618; 142552</t>
+          <t>101537; 143561</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93995; 132924</t>
+          <t>92424; 136335</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>125912; 176684</t>
+          <t>128892; 177626</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>106526; 149513</t>
+          <t>107448; 149838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>193787; 250744</t>
+          <t>188699; 248008</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>156692; 208851</t>
+          <t>156000; 212186</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>239110; 296801</t>
+          <t>231548; 296524</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>164412; 217366</t>
+          <t>164340; 218178</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>311936; 386535</t>
+          <t>315960; 387073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>283875; 351976</t>
+          <t>288562; 356536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310253; 443635</t>
+          <t>294988; 442832</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>238111; 297241</t>
+          <t>235995; 297745</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>395711; 474950</t>
+          <t>397571; 482700</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>351406; 430726</t>
+          <t>348835; 426247</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>491218; 1258568</t>
+          <t>486816; 1202240</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>413344; 500464</t>
+          <t>420869; 502330</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>734156; 840868</t>
+          <t>731552; 845405</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>655378; 761595</t>
+          <t>655952; 761295</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>874918; 1732706</t>
+          <t>867714; 1724811</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A15-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,8</t>
+          <t>4,28; 7,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,76; 14,77</t>
+          <t>9,84; 15,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 14,59</t>
+          <t>9,32; 14,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 16,42</t>
+          <t>11,25; 16,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 10,55</t>
+          <t>6,32; 10,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,39; 16,47</t>
+          <t>11,25; 16,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,43</t>
+          <t>11,14; 16,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,7; 17,52</t>
+          <t>13,41; 17,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 8,58</t>
+          <t>5,94; 8,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,26; 14,93</t>
+          <t>11,14; 14,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 14,52</t>
+          <t>10,88; 14,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,29; 16,44</t>
+          <t>13,0; 16,02</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,54</t>
+          <t>4,53; 7,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 12,06</t>
+          <t>8,26; 12,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,65</t>
+          <t>7,8; 11,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,9</t>
+          <t>9,43; 13,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 11,12</t>
+          <t>7,29; 11,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,77</t>
+          <t>9,76; 13,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,05; 14,39</t>
+          <t>10,0; 14,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,1; 15,43</t>
+          <t>11,77; 15,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,67</t>
+          <t>6,3; 8,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 12,23</t>
+          <t>9,4; 12,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 12,45</t>
+          <t>9,4; 12,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 12,96</t>
+          <t>11,13; 13,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,41</t>
+          <t>3,96; 7,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 11,56</t>
+          <t>7,05; 11,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 11,76</t>
+          <t>7,56; 11,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 15,1</t>
+          <t>9,92; 14,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,66</t>
+          <t>5,69; 9,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,37; 15,28</t>
+          <t>10,33; 15,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,08</t>
+          <t>6,06; 10,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 67,95</t>
+          <t>9,71; 13,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,84</t>
+          <t>5,16; 7,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,45; 12,83</t>
+          <t>9,31; 12,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,11</t>
+          <t>7,29; 10,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,22; 53,33</t>
+          <t>10,34; 13,28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,64</t>
+          <t>4,61; 7,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,41</t>
+          <t>8,41; 12,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,36</t>
+          <t>5,97; 9,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 14,48</t>
+          <t>10,2; 13,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,62</t>
+          <t>5,3; 8,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 13,69</t>
+          <t>9,77; 13,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 13,06</t>
+          <t>8,83; 12,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,81; 16,28</t>
+          <t>13,54; 16,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,56</t>
+          <t>5,35; 7,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 12,43</t>
+          <t>9,59; 12,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 10,71</t>
+          <t>7,9; 10,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 14,69</t>
+          <t>12,47; 14,94</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,66</t>
+          <t>5,02; 6,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 11,31</t>
+          <t>9,3; 11,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,5; 10,5</t>
+          <t>8,36; 10,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,8</t>
+          <t>11,04; 12,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,81</t>
+          <t>7,0; 8,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,21; 13,61</t>
+          <t>11,21; 13,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,84; 12,03</t>
+          <t>10,02; 12,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,31; 32,87</t>
+          <t>13,03; 14,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,55</t>
+          <t>6,31; 7,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 12,13</t>
+          <t>10,59; 12,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 10,97</t>
+          <t>9,47; 10,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,19; 24,24</t>
+          <t>12,28; 13,68</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87809</t>
+          <t>93466</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>105465</t>
+          <t>111801</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>193274</t>
+          <t>205267</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29311; 54036</t>
+          <t>29639; 53935</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68418; 103494</t>
+          <t>68981; 105259</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63407; 98425</t>
+          <t>62893; 96583</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73702; 104358</t>
+          <t>77733; 110977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43981; 72627</t>
+          <t>43506; 71836</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79059; 114348</t>
+          <t>78140; 114515</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73559; 110567</t>
+          <t>74922; 111742</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92554; 118369</t>
+          <t>98285; 125549</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81217; 118564</t>
+          <t>82104; 119896</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>157139; 208226</t>
+          <t>155471; 206372</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147248; 195741</t>
+          <t>146619; 195471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>174228; 215501</t>
+          <t>185049; 228157</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107629</t>
+          <t>116546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>130610</t>
+          <t>143478</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>238239</t>
+          <t>260024</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43043; 72518</t>
+          <t>43569; 73806</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82654; 122715</t>
+          <t>84112; 122826</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79345; 119161</t>
+          <t>79702; 116534</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52008; 141963</t>
+          <t>98937; 137148</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71671; 107678</t>
+          <t>70632; 106649</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99670; 141358</t>
+          <t>100209; 142010</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>104809; 150120</t>
+          <t>104320; 150184</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>115976; 147792</t>
+          <t>126042; 160715</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120728; 167439</t>
+          <t>121613; 168446</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>191784; 250064</t>
+          <t>192188; 251210</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>194530; 257100</t>
+          <t>194188; 252527</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153933; 278718</t>
+          <t>235866; 284902</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85896</t>
+          <t>95757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>287176</t>
+          <t>93013</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>373072</t>
+          <t>188770</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26847; 50249</t>
+          <t>26850; 49719</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53036; 87444</t>
+          <t>53315; 88532</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56893; 89350</t>
+          <t>57456; 89720</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70579; 106265</t>
+          <t>79551; 115067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39356; 66082</t>
+          <t>38895; 64362</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80475; 118619</t>
+          <t>80226; 121401</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46007; 79136</t>
+          <t>47535; 79025</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>99049; 633866</t>
+          <t>78786; 108862</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71083; 106766</t>
+          <t>70350; 107406</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144847; 196667</t>
+          <t>142698; 195563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114429; 156183</t>
+          <t>112522; 159579</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>183671; 872737</t>
+          <t>166919; 214261</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114604</t>
+          <t>117725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>155156</t>
+          <t>170038</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>269761</t>
+          <t>287764</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44129; 71954</t>
+          <t>43433; 70377</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76174; 117381</t>
+          <t>79524; 117287</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55639; 87750</t>
+          <t>55994; 86526</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>98066; 134176</t>
+          <t>101001; 136766</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56264; 89563</t>
+          <t>55001; 88900</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>101537; 143561</t>
+          <t>102429; 146307</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92424; 136335</t>
+          <t>92165; 135180</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>128892; 177626</t>
+          <t>151251; 188706</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>107448; 149838</t>
+          <t>105959; 148745</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>188699; 248008</t>
+          <t>191200; 248553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>156000; 212186</t>
+          <t>156580; 210809</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>231548; 296524</t>
+          <t>262714; 314716</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>395938</t>
+          <t>423495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>678408</t>
+          <t>518329</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1074346</t>
+          <t>941824</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>164340; 218178</t>
+          <t>164565; 216536</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>315960; 387073</t>
+          <t>318298; 393069</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>288562; 356536</t>
+          <t>283741; 351265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>294988; 442832</t>
+          <t>390015; 458262</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>235995; 297745</t>
+          <t>236389; 297601</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>397571; 482700</t>
+          <t>397636; 475543</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>348835; 426247</t>
+          <t>355114; 430273</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>486816; 1202240</t>
+          <t>486233; 551151</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>420869; 502330</t>
+          <t>419808; 496259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>731552; 845405</t>
+          <t>738161; 841006</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>655952; 761295</t>
+          <t>657075; 762250</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>867714; 1724811</t>
+          <t>891729; 993896</t>
         </is>
       </c>
     </row>
